--- a/DOC/인사평가_성과평가표_김동현_2026년_수정.xlsx
+++ b/DOC/인사평가_성과평가표_김동현_2026년_수정.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\성과관리\2026년도\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nullnet\Documents\Amaranth10\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="성과평가표" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="autoNoTable"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -272,67 +272,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>테스트 자동화 확대를 통한 업무 효율성 향상
-  - Nexacro K 테스트 케이스 자동화 개발
-      -&gt; 2026년 3분기까지 진행했던 Nexacro K 테스트 케이스를 기반으로 TestPro 케이스를 2026년 11월 말까지 작성 완료한다.
-      -&gt; TestPro로 작성이 불가능한 케이스를 제외한다.
-  - 접수 요구사항에 대한 테스트 자동화 확대
-      -&gt; Nexacro N v21, Nexacro N v24 건 대상으로 진행한다.
-      -&gt; TestPro로 작성이 불가능한 케이스를 제외한다.
-      -&gt; 목표율은 (4월 1일부터 11월 말까지 TOPS에 Nexacro N v21 &amp; v24 접수 건) - (TestPro로 작성 불가능한 건) = 총 대상 건에서 75% 이상 TestPro 케이스 
-S : Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화 확대를 완료하고  목표율을 95% 이상 달성
-A : B항목을 달성하며 Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화의 목표율까지 달성
-B : Nexacro K 테스트 케이스 자동화 개발 일정을 달성하며 접수 요구사항에 대한 테스트 자동화 확대를 진행
-C : Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화 진행을 일정에 맞게 진행하되 완료 목표율까지는 미달성
-D : Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화 일정 및 완료 목표율 미달성</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NexaLAP 출시를 위한 초기 품질 확보 및 운영 체계 구축
-  - 유지보수 프로세스 구축
-S : 없음
-A : NexaLAP 정식 배포버전 출시 전 NexaLAP 유지보수 프로세스를 연관 부서와 협의를 진행하며 문서화를 통하여 정의
-B : NexaLAP 정식 배포버전 출시 전 NexaLAP 유지보수 프로세스를 기존 제품 수준의 유지보수 체계와 준용하게 운용할 수 있도록 연관 부서와 협의를 진행
-C : 3분기까지 NexaLAP 유지보수 프로세스를 기존 제품 수준의 유지보수 체계와 준용하게 운용할 수 있도록 연관 부서와 협의를 진행
-D : 미진행</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nexacro K 안정적 출시를 위한 품질 체계 구축
-  - 신규 기능 테스트 개발 및 수행
-S : 없음
-A : B항목을 달성하며 테스트 과정에서 발견된 개선 필요 사항과 스펙 외 기능 개선 아이디어를 도출하여 제품 품질 향상 지원
-B : 배정된 신규 기능 테스트를 수립된 일정에 맞게 진행
-C : 배정된 신규 기능 테스트를 진행
-D : 미진행
-테스트 일정 시 외부 요소(긴급 대응, 이슈 사이트 발생, 개인 사유)로 인하여 일정에 문제가 발생 시 상급자가 판단하여 평가를 한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">요구 사항 관리 효율성 제고
-  - 신규/변경 목록 관리 시스템 구축
-  - 긴급 관리 기능 고도화를 통한 고객대응력 향상
-S :  A목표를 달성하고 운영을 진행여 관련부서와 공유
-A :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행을  3분기까지 완료 
-B :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행을 12월 말까지 완료   
-C :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행 둘중에 한개를 완료
-D :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행 둘다 미달성 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>접근성 기능 테스트 자동화 구축 및 고도화
-  - PM으로 자동화 구축의 방향성을 제시하고 2026년도 9월까지 프로젝트 완료를 목표로 관리를 진행한다.
-  - 완료 목표는 접근성 지원 컴포넌트 와  TOPS에 접수된 접근성 요구사항을 대상으로 자동화를 진행한다 
-  - 자동화 구축 개발자(이혜림)의 성취도에 따라서 평가된다.
-  - 프로젝트 완료 이후 개선 사항이 발생 시 spot으로 진행을 한다.
-S : A항목을 달성하며 프로젝트 개발자(이혜림)의 달성률이 S일 때
-A : B항목을 달성하며 2026년 11월 말까지 접근성 심사 진행 프로젝트 소스 기반으로 접근성 테스트 케이스를 추가할 수 있도록 관리 및 지원
-B : 접근성 기능 테스트 자동화 구축 및 고도화 작업 프로젝트 완료 목표일까지 완료될 수 있도록 관리 및 지원
-C : 접근성 기능 테스트 자동화 구축 및 고도화 작업을 진행하되 프로젝트 완료 목표일에는 미달성
-D : 미진행</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>기본역량</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -343,7 +282,7 @@
   <si>
     <r>
       <t xml:space="preserve">정기 테스트 지원
-</t>
+ </t>
     </r>
     <r>
       <rPr>
@@ -367,11 +306,186 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>S :  없음 
+      <t xml:space="preserve">S :  없음 
 A :  B목표를 요청날짜보다 일정 단축 
 B :  QA파트에서 정기 테스트 지원 요청 목록을 지정된 날짜가지 완료    
 C :  B 실패
-D :  미달성</t>
+D :  미달성
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--&gt; 기본역량 (근태, 협력, 태도 등)에 대한 평가자 정성평가 점수를 포함하여 점수 산정함 추가해주세요.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">요구 사항 관리 효율성 제고
+  - 신규/변경 목록 관리 시스템 구축
+  - 긴급 관리 기능 고도화를 통한 고객대응력 향상
+S :  없음 
+A :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행을  3분기까지 완료 
+B :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행을 12월 말까지 완료   
+C :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행 둘중에 한개를 완료
+D :  신규/변경 목록 관리 시스템 구축 &amp; 긴급 관리 기능 고도화 진행 둘다 미달성 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--&gt; 11월까지 완료 목표 해주면 어떨까요? 또는 두개 중 하나를 먼저 이른 시간에 완료하는 걸 B로 하고 2개 다를 11월까지 완료하면 A 이런건 어떨까요?
+    고도화의 기준은 현재 보다 관리가 나아졌다(누락이 없거나, 찾기 쉽워 업무에 도움이 됐다는 판단)는 외부 평가로 정성평가를 포함할 수 밖에 없을 듯 한데. 의견 주세요.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">테스트 자동화 확대를 통한 업무 효율성 향상
+  - Nexacro K 테스트 케이스 자동화 개발
+      -&gt; 2026년 3분기까지 진행했던 Nexacro K 테스트 케이스를 기반으로 TestPro 케이스를 2026년 11월 말까지 작성 완료한다.
+      -&gt; TestPro로 작성이 불가능한 케이스를 제외한다.
+  - 접수 요구사항에 대한 테스트 자동화 확대
+      -&gt; Nexacro N v21, Nexacro N v24 건 대상으로 진행한다.
+      -&gt; TestPro로 작성이 불가능한 케이스를 제외한다.
+      -&gt; 목표율은 (4월 1일부터 11월 말까지 TOPS에 Nexacro N v21 &amp; v24 접수 건) - (TestPro로 작성 불가능한 건) = 총 대상 건에서 75% 이상 TestPro 케이스 
+S : A항목을 달성하고   접수 요구사항에 대한 테스트 자동화 전환 목표율을 95% 이상 달성
+A : B항목을 달성하며 Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화의 목표율까지 달성
+B : Nexacro K 테스트 케이스 자동화 개발 일정을 달성하며 접수 요구사항에 대한 테스트 자동화 확대를 진행
+C : Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화 진행을 일정에 맞게 진행하되 완료 목표율까지는 미달성
+D : Nexacro K 테스트 케이스 자동화 개발과 접수 요구사항에 대한 테스트 자동화 일정 및 완료 목표율 미달성
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--&gt; 접수 요구사항에 대한 테스트 자동화 확대부터 발생하는걸 위주로 해주세요. 기존에 있는건 QC 파트 인원들이 작업 할 수 있게 하려고 합니다.
+     예) 접수 건 중 디그라데이션 판정 시 + @day 안에 작성 또는 프리징 전까지 완료율
+     두가지를 따로 지표를 만들고 평가 할 수 있게 해주세요. 한꺼번에 넣으면 평가가 더 힘들어질꺼 같습니다.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">접근성 기능 테스트 자동화 구축 및 고도화
+  - PM으로 자동화 구축의 방향성을 제시하고 2026년도 9월까지 프로젝트 완료를 목표로 관리를 진행한다.
+  - 완료 목표는 접근성 지원 컴포넌트 와  TOPS에 접수된 접근성 요구사항을 대상으로 자동화를 진행한다 
+  - 자동화 구축 개발자(이혜림)의 달성률에 따라 평가된다 
+S : A항목을 달성하며 프로젝트 개발자(이혜림)의 달성률이 S이여야함, 접근성 기능 테스트 자동화 테스트 구축 완료 및 운영까지 2026년 10월까지 진행한다 
+A : B항목을 달성하며 2026년 11월 말까지 접근성 심사 진행 프로젝트 소스 기반으로 접근성 테스트 케이스(시나리오기반) 를 추가할 수 있도록 관리 및 지원
+B : 접근성 기능 테스트 자동화 구축 및 고도화 작업 프로젝트 완료 목표일까지 완료될 수 있도록 관리 및 지원
+C : 접근성 기능 테스트 자동화 구축 및 고도화 작업을 진행하되 프로젝트 완료 목표일에는 미달성
+D : 미진행
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">--&gt; 관리 및 지원이라는 표현보다는 완료로 마무리 될 수 있도록 해주세요. 관리 및 지원을 통한 완료 라든지. 어쨌튼 둘의 목표가 완료가 되도록.
+    S는 빼주세요. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nexacro K 안정적 출시를 위한 품질 체계 구축
+  - 신규 기능 테스트 개발 및 수행
+S : 없음
+A : B항목을 달성하며 테스트 과정에서 발견된 개선 필요 사항과 스펙 외 기능 개선 아이디어를 도출하여 제품 품질 향상 지원
+B : 배정된 신규 기능 테스트를 수립된 일정에 맞게 진행
+C : 배정된 신규 기능 테스트를 진행
+D : 미진행
+테스트 일정 시 외부 요소(긴급 대응, 이슈 사이트 발생, 개인 사유)로 인하여 일정에 문제가 발생 시 상급자가 판단하여 평가를 한다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">예)
+S : 
+A : 테스트 일정이 앞당겨 수행 완료하며 자동화 작업까지 완료한 경우
+B : 테스트를 일정에 맞게 100% 수행한 경우
+C : 테스트 케이스 개발 또는 테스트 수행을 80% 수행한 경우
+D : 테스트 케이스 개발을 완료하지 못하거나, 테스트 수행을 제대로 하지 못한 경우 (테스트 수행이 제대로 되지 않았다고 판단된 경우) </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NexaLAP 출시를 위한 초기 품질 확보 및 운영 체계 구축
+  - 유지보수 프로세스 구축
+S : 없음
+A : NexaLAP 정식 배포버전 출시 전 NexaLAP 유지보수 프로세스를 연관 부서와 협의를 진행하며 문서화를 통하여 정의
+B : NexaLAP 정식 배포버전 출시 전 NexaLAP 유지보수 프로세스를 기존 제품 수준의 유지보수 체계와 준용하게 운용할 수 있도록 연관 부서와 협의를 진행
+C : 3분기까지 NexaLAP 유지보수 프로세스를 기존 제품 수준의 유지보수 체계와 준용하게 운용할 수 있도록 연관 부서와 협의를 진행
+D : 미진행
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--&gt; B에 협의 진행이 목표가 아니라 구축이 목표입니다. 구축 완료가 B가 되도록 해주세요</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -383,7 +497,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,6 +656,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -851,7 +973,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -952,6 +1074,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1008,6 +1134,51 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1067,51 +1238,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1413,100 +1539,100 @@
   <sheetData>
     <row r="1" spans="1:19" ht="69.95" customHeight="1">
       <c r="A1" s="11"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
     </row>
     <row r="2" spans="1:19" ht="33" customHeight="1">
       <c r="A2" s="11"/>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="50" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="45" t="s">
+      <c r="E2" s="63"/>
+      <c r="F2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="50" t="s">
+      <c r="G2" s="60"/>
+      <c r="H2" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="45" t="s">
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="47"/>
-      <c r="M2" s="50" t="s">
+      <c r="L2" s="60"/>
+      <c r="M2" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="50"/>
-      <c r="O2" s="45" t="s">
+      <c r="N2" s="63"/>
+      <c r="O2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="50" t="s">
+      <c r="P2" s="60"/>
+      <c r="Q2" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="R2" s="51"/>
+      <c r="R2" s="64"/>
     </row>
     <row r="3" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A3" s="13"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
     </row>
     <row r="4" spans="1:19" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="11"/>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="43" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="44"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1516,196 +1642,206 @@
       <c r="N4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="53" t="s">
+      <c r="O4" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="44"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="57"/>
     </row>
     <row r="5" spans="1:19" ht="33" customHeight="1">
       <c r="A5" s="11"/>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="36" t="s">
+      <c r="D5" s="30"/>
+      <c r="E5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="39"/>
       <c r="L5" s="26"/>
-      <c r="M5" s="26">
-        <v>0.1</v>
+      <c r="M5" s="27">
+        <v>0.2</v>
       </c>
       <c r="N5" s="9">
         <f>L5*M5</f>
         <v>0</v>
       </c>
-      <c r="O5" s="29"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
     </row>
     <row r="6" spans="1:19" ht="33" customHeight="1">
       <c r="A6" s="11"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="36" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="39"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5">
+        <v>0.2</v>
+      </c>
       <c r="N6" s="9">
         <f t="shared" ref="N6:N10" si="0">L6*M6</f>
         <v>0</v>
       </c>
-      <c r="O6" s="29"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
     </row>
     <row r="7" spans="1:19" ht="33" customHeight="1">
       <c r="A7" s="11"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="36" t="s">
+      <c r="D7" s="30"/>
+      <c r="E7" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="39"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="5">
+        <v>0.2</v>
+      </c>
       <c r="N7" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O7" s="29"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
     </row>
     <row r="8" spans="1:19" ht="33" customHeight="1">
       <c r="A8" s="11"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="36" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="39"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="5">
+        <v>0.1</v>
+      </c>
       <c r="N8" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O8" s="27"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="29"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="30"/>
     </row>
     <row r="9" spans="1:19" ht="33" customHeight="1">
       <c r="A9" s="11"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="68"/>
+      <c r="C9" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="36" t="s">
+      <c r="D9" s="30"/>
+      <c r="E9" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="39"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="5">
+        <v>0.2</v>
+      </c>
       <c r="N9" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
     </row>
     <row r="10" spans="1:19" ht="33" customHeight="1">
       <c r="A10" s="11"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="38"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="39"/>
       <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="M10" s="6">
+        <v>0.1</v>
+      </c>
       <c r="N10" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
     </row>
     <row r="11" spans="1:19" ht="33" customHeight="1" thickBot="1">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="67"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="53"/>
       <c r="M11" s="18">
         <f>SUM(M5:M10)</f>
-        <v>0.1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="N11" s="10">
         <f>SUM(N5:N10)</f>
@@ -1731,17 +1867,17 @@
     </row>
     <row r="14" spans="1:19" s="15" customFormat="1" ht="36.950000000000003" customHeight="1">
       <c r="A14" s="11"/>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="44"/>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="61" t="s">
+      <c r="E14" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="62"/>
+      <c r="F14" s="48"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -1758,15 +1894,15 @@
     </row>
     <row r="15" spans="1:19" s="15" customFormat="1" ht="36.950000000000003" customHeight="1" thickBot="1">
       <c r="A15" s="11"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="60"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="64"/>
+      <c r="F15" s="50"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -1928,165 +2064,165 @@
       <c r="O23" s="20"/>
     </row>
     <row r="27" spans="2:18">
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="45" t="s">
+      <c r="C27" s="57"/>
+      <c r="D27" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="47"/>
-    </row>
-    <row r="28" spans="2:18" ht="111.75" customHeight="1">
-      <c r="B28" s="39" t="s">
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="59"/>
+      <c r="R27" s="60"/>
+    </row>
+    <row r="28" spans="2:18" ht="190.5" customHeight="1">
+      <c r="B28" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="40"/>
-    </row>
-    <row r="29" spans="2:18" ht="136.5" customHeight="1">
-      <c r="B29" s="39" t="s">
+      <c r="C28" s="40"/>
+      <c r="D28" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+    </row>
+    <row r="29" spans="2:18" ht="204" customHeight="1">
+      <c r="B29" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="40" t="s">
+      <c r="C29" s="40"/>
+      <c r="D29" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+    </row>
+    <row r="30" spans="2:18" ht="177" customHeight="1">
+      <c r="B30" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+    </row>
+    <row r="31" spans="2:18" ht="297" customHeight="1">
+      <c r="B31" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="32"/>
+      <c r="D31" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="35"/>
+    </row>
+    <row r="32" spans="2:18" ht="180.75" customHeight="1">
+      <c r="B32" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+    </row>
+    <row r="33" spans="2:18" ht="168" customHeight="1">
+      <c r="B33" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="40"/>
+      <c r="D33" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="40"/>
-    </row>
-    <row r="30" spans="2:18" ht="177" customHeight="1">
-      <c r="B30" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="40"/>
-    </row>
-    <row r="31" spans="2:18" ht="257.25" customHeight="1">
-      <c r="B31" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="34"/>
-    </row>
-    <row r="32" spans="2:18" ht="139.5" customHeight="1">
-      <c r="B32" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="40"/>
-    </row>
-    <row r="33" spans="2:18" ht="100.5" customHeight="1">
-      <c r="B33" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="40"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="40"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="50">
